--- a/docs/test-cases/TC_Kalender_Tambah.xlsx
+++ b/docs/test-cases/TC_Kalender_Tambah.xlsx
@@ -661,7 +661,7 @@
       </c>
       <c r="D4" s="3" t="inlineStr">
         <is>
-          <t>Login admin; ada instansi tanpa kalender; file `cypress/fixtures/kalender/header-valid.jpg` (&lt;2MB) tersedia</t>
+          <t>Login admin; ada instansi tanpa kalender; file `cypress/fixtures/kalender/header-valid.png` (&lt;2MB) tersedia</t>
         </is>
       </c>
       <c r="E4" s="3" t="inlineStr">
@@ -670,14 +670,14 @@
 2) Pilih Instansi
 3) Pilih Awal pekan dimulai = Senin
 4) Pilih Nama Pekan = Minggu
-5) Upload header-valid.jpg (&lt;2MB)
+5) Upload header-valid.png (&lt;2MB)
 6) Tunggu preview file muncul (card dengan nama file)
 7) Klik "Simpan"</t>
         </is>
       </c>
       <c r="F4" s="3" t="inlineStr">
         <is>
-          <t>Instansi=&lt;instansi tanpa kalender&gt;; Awal pekan=Senin; Nama Pekan=Minggu; Header=header-valid.jpg</t>
+          <t>Instansi=&lt;instansi tanpa kalender&gt;; Awal pekan=Senin; Nama Pekan=Minggu; Header=header-valid.png</t>
         </is>
       </c>
       <c r="G4" s="3" t="inlineStr">
@@ -692,12 +692,12 @@
       </c>
       <c r="I4" s="3" t="inlineStr">
         <is>
-          <t>Belum dijalankan</t>
+          <t>FAIL</t>
         </is>
       </c>
       <c r="J4" s="3" t="inlineStr">
         <is>
-          <t>Verifikasi persist via reload + cek img src kolom Header bukan default URL</t>
+          <t>BUG-026 — Upload sukses (toast &amp; modal close) tapi kolom Header kosong (text "-"). Regresi: sebelumnya berfungsi</t>
         </is>
       </c>
     </row>
